--- a/data/export/2026-10-31-operations.xlsx
+++ b/data/export/2026-10-31-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,7 +2394,7 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -2363,22 +2407,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2416,7 +2460,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2466,7 +2510,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2523,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2571,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2590,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,7 +2626,7 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -2595,22 +2639,22 @@
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2687,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2706,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2742,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2764,7 +2808,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2822,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2858,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2880,7 +2924,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2938,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,35 +2974,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2991,12 +3035,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3010,7 +3054,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3046,7 +3090,2907 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55575A</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A59793A</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A57383A</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-operations.xlsx
+++ b/data/export/2026-10-31-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD47"/>
+  <dimension ref="A1:AD64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -901,19 +901,19 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1141,19 +1149,19 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:47</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1835,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1868,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1892,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1912,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2042,7 +2094,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2199,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2157,12 +2209,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2280,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2396,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,41 +2440,45 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2455,12 +2511,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2474,7 +2530,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2499,46 +2555,50 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2571,12 +2631,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2590,7 +2650,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2615,46 +2675,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2687,12 +2751,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2706,7 +2770,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2731,46 +2795,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2803,12 +2871,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2822,7 +2890,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2847,46 +2915,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2919,12 +2991,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2938,7 +3010,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2963,46 +3035,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3035,12 +3111,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3054,7 +3130,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3079,46 +3155,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3151,12 +3231,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3170,7 +3250,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3195,18 +3275,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3303,7 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3229,7 +3313,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3239,40 +3323,44 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3286,7 +3374,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3296,17 +3384,17 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3316,13 +3404,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3427,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3345,7 +3437,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3355,40 +3447,44 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3402,7 +3498,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3412,17 +3508,17 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3432,13 +3528,17 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3551,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3461,7 +3561,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3471,40 +3571,44 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3518,7 +3622,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3528,17 +3632,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3548,13 +3652,17 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -3567,22 +3675,22 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3615,12 +3723,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3634,7 +3742,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3670,7 +3778,7 @@
       <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3791,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3693,7 +3801,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3703,40 +3811,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3750,7 +3862,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3760,17 +3872,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3780,13 +3892,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -3799,22 +3915,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3847,12 +3963,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3866,7 +3982,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3902,7 +4018,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -3915,22 +4031,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3963,12 +4079,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3982,7 +4098,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4018,7 +4134,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4031,22 +4147,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4079,12 +4195,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4098,7 +4214,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4134,7 +4250,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4147,22 +4263,22 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A55575A</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4195,12 +4311,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4214,7 +4330,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4250,7 +4366,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4263,7 +4379,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A59793A</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4273,7 +4389,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4311,12 +4427,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4330,7 +4446,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4366,7 +4482,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4495,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4389,7 +4505,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4427,12 +4543,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4446,7 +4562,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4482,7 +4598,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4495,22 +4611,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A57383A</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4543,12 +4659,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4562,7 +4678,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4598,7 +4714,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -4611,7 +4727,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4621,7 +4737,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4659,12 +4775,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4678,7 +4794,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4714,35 +4830,35 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4775,12 +4891,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4794,7 +4910,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4819,7 +4935,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4830,35 +4946,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4891,12 +5007,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4910,7 +5026,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4935,7 +5051,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4946,35 +5062,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55575A</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5007,12 +5123,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5026,7 +5142,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5062,35 +5178,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59793A</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5123,12 +5239,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5142,7 +5258,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5178,35 +5294,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5239,12 +5355,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5258,7 +5374,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5294,35 +5410,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A57383A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5355,12 +5471,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5374,7 +5490,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5410,35 +5526,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5471,12 +5587,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5490,7 +5606,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5526,35 +5642,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5587,12 +5703,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5606,7 +5722,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5631,7 +5747,7 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5642,35 +5758,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5703,12 +5819,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5722,7 +5838,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5758,35 +5874,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5819,12 +5935,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5838,7 +5954,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5874,35 +5990,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5935,12 +6051,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5954,7 +6070,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5979,7 +6095,7 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -5990,7 +6106,2043 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A57601A</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>08:36</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>6/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>2/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>3/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>—/11</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:13</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>1/11</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-operations.xlsx
+++ b/data/export/2026-10-31-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD64"/>
+  <dimension ref="A1:AD93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1893,24 +1893,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1969,12 +1969,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2007,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2040,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2064,37 +2068,37 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2127,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2160,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,7 +2212,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2247,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -2280,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2304,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2363,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2396,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2420,32 +2440,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2483,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2516,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2540,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2636,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2660,37 +2688,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
@@ -2723,32 +2751,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2756,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2780,32 +2812,32 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -2876,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2996,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3035,7 +3067,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3050,7 +3082,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3148,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3155,7 +3187,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3183,22 +3215,22 @@
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3236,7 +3268,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3250,7 +3282,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3280,87 +3312,83 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3374,7 +3402,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3384,107 +3412,103 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3498,7 +3522,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3508,107 +3532,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3622,7 +3642,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3632,65 +3652,65 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3723,12 +3743,12 @@
       <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3742,7 +3762,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3767,88 +3787,88 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>70.5</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3862,7 +3882,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3872,65 +3892,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3963,12 +3983,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3982,7 +4002,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4007,46 +4027,50 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4079,12 +4103,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4098,7 +4122,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4123,46 +4147,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4195,12 +4223,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4214,7 +4242,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4239,18 +4267,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -4263,60 +4295,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4330,7 +4366,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4340,33 +4376,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4379,60 +4419,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4446,7 +4490,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4456,33 +4500,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -4495,60 +4543,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4562,7 +4614,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4572,33 +4624,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
@@ -4611,60 +4667,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4678,7 +4738,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4688,33 +4748,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4791,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4737,7 +4801,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4747,40 +4811,44 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4794,7 +4862,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4804,33 +4872,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4915,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4853,7 +4925,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4863,40 +4935,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4910,7 +4986,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4920,33 +4996,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/26</t>
         </is>
       </c>
     </row>
@@ -4959,7 +5039,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4969,7 +5049,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4979,40 +5059,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5026,7 +5110,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5036,33 +5120,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5163,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A55575A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5085,7 +5173,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5095,40 +5183,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5142,7 +5234,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5152,17 +5244,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5172,13 +5264,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -5191,60 +5287,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A59793A</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5258,7 +5358,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5268,33 +5368,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>11/26</t>
         </is>
       </c>
     </row>
@@ -5307,60 +5411,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5374,7 +5482,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5384,17 +5492,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5404,13 +5512,17 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>5/26</t>
         </is>
       </c>
     </row>
@@ -5423,60 +5535,64 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A57383A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5490,7 +5606,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5500,33 +5616,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/26</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5659,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5549,7 +5669,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5559,12 +5679,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq60，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5587,12 +5707,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5600,13 +5720,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:08</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5642,7 +5778,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5655,60 +5791,64 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5722,7 +5862,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5732,17 +5872,17 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5752,13 +5892,17 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC44" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/26</t>
         </is>
       </c>
     </row>
@@ -5771,22 +5915,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5819,12 +5963,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5838,7 +5982,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5874,7 +6018,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -5887,22 +6031,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5935,12 +6079,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5954,7 +6098,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5990,7 +6134,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6003,22 +6147,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A55575A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6051,12 +6195,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6070,7 +6214,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6106,7 +6250,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6263,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A57601A</t>
+          <t>沪A59793A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6129,7 +6273,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6167,12 +6311,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6186,7 +6330,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6222,35 +6366,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6283,12 +6427,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6302,7 +6446,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6327,7 +6471,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6338,77 +6482,73 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A57383A</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6422,7 +6562,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6432,107 +6572,99 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6546,7 +6678,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6556,107 +6688,99 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6670,7 +6794,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6680,107 +6804,99 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6794,7 +6910,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6804,99 +6920,91 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6904,7 +7012,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6918,7 +7026,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6928,17 +7036,17 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6948,87 +7056,79 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7042,7 +7142,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7052,17 +7152,17 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7072,45 +7172,41 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A57601A</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7148,7 +7244,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7162,7 +7258,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7187,7 +7283,7 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7198,35 +7294,35 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7259,12 +7355,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7278,7 +7374,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7303,46 +7399,50 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7375,12 +7475,12 @@
       <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7394,7 +7494,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7419,46 +7519,50 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -7491,12 +7595,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7510,7 +7614,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7535,50 +7639,46 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>—/26</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7616,7 +7716,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7630,7 +7730,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7665,40 +7765,40 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>1/26</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7731,12 +7831,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7750,7 +7850,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7775,46 +7875,50 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/26</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7847,12 +7951,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7866,7 +7970,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7901,40 +8005,40 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>10/26</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7967,12 +8071,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7986,7 +8090,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8011,46 +8115,50 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/26</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8083,12 +8191,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:13</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8102,47 +8210,3547 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>11/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>2/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>6/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A30260D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W64" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X64" s="2" t="inlineStr">
+      <c r="X81" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y64" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z64" s="2" t="inlineStr">
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
+      <c r="AB82" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AD64" s="2" t="inlineStr">
-        <is>
-          <t>1/11</t>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A30829D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35683D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A51582D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A50235D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-operations.xlsx
+++ b/data/export/2026-10-31-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD93"/>
+  <dimension ref="A1:AD95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2875,32 +2875,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2908,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2932,17 +2936,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2952,17 +2956,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3082,7 +3086,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3268,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3322,7 +3326,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3392,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3442,7 +3446,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3562,7 +3566,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>9/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3752,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3868,7 +3872,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3922,7 +3926,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3992,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4037,7 +4041,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
@@ -4108,7 +4112,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4228,7 +4232,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4282,7 +4286,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4356,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4406,7 +4410,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4476,7 +4480,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4530,7 +4534,7 @@
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4604,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4654,7 +4658,7 @@
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -4724,7 +4728,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4778,7 +4782,7 @@
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4848,7 +4852,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4902,7 +4906,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4976,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5026,7 +5030,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -5096,7 +5100,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5150,7 +5154,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5278,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5348,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5398,7 +5402,7 @@
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5526,7 @@
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>5/26</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5596,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5646,7 +5650,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5782,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5821,24 +5825,24 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5848,7 +5852,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5887,22 +5891,22 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>12/26</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6022,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6051,32 +6055,36 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6084,7 +6092,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6108,17 +6116,17 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6128,13 +6136,17 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6212,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6250,7 +6262,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6328,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6366,7 +6378,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6494,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6560,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6598,7 +6610,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6664,7 +6676,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6714,7 +6726,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6792,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6830,7 +6842,7 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6958,7 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7074,7 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7140,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7178,7 +7190,7 @@
       <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7256,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7294,7 +7306,7 @@
       <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7372,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7414,7 +7426,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7492,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7534,7 +7546,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -7600,7 +7612,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7650,7 +7662,7 @@
       <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7728,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7770,7 +7782,7 @@
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>1/26</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7848,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7890,7 +7902,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>3/26</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7968,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8010,7 +8022,7 @@
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>10/26</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8088,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8130,7 +8142,7 @@
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>8/26</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -8196,7 +8208,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8250,7 +8262,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>11/26</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8328,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8370,7 +8382,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>2/26</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -8383,22 +8395,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8431,12 +8443,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:32</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8450,7 +8462,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8475,50 +8487,46 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>6/26</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8551,12 +8559,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:32</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8570,7 +8578,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8595,7 +8603,7 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
@@ -8605,82 +8613,78 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8694,7 +8698,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8704,22 +8708,22 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
@@ -8729,12 +8733,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8751,7 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -8757,7 +8761,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -8767,36 +8771,32 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8818,7 +8818,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8828,17 +8828,17 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8848,17 +8848,17 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8871,7 +8871,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8977,12 +8977,12 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -9025,24 +9025,24 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9066,7 +9066,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9091,22 +9091,22 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9149,34 +9149,34 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
@@ -9225,12 +9225,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9243,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9273,34 +9273,34 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9367,7 +9367,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9397,24 +9397,24 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
@@ -9424,7 +9424,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9438,7 +9438,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9491,7 +9491,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9521,34 +9521,34 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9562,7 +9562,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9615,7 +9615,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9645,34 +9645,34 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9686,7 +9686,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9711,7 +9711,7 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
@@ -9721,12 +9721,12 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9759,40 +9759,44 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9806,7 +9810,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9816,22 +9820,22 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
@@ -9841,12 +9845,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9859,7 +9863,7 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -9869,7 +9873,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -9889,34 +9893,34 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9930,7 +9934,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9955,22 +9959,22 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9983,22 +9987,22 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -10031,12 +10035,12 @@
       <c r="N79" s="2" t="inlineStr"/>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10050,7 +10054,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10075,18 +10079,22 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10099,60 +10107,64 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10166,7 +10178,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10176,17 +10188,17 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10196,12 +10208,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10219,22 +10231,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A30260D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10267,12 +10279,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10286,7 +10298,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10335,22 +10347,22 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -10383,12 +10395,12 @@
       <c r="N82" s="2" t="inlineStr"/>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10402,7 +10414,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10427,7 +10439,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10437,12 +10449,12 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10455,22 +10467,22 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A30829D</t>
+          <t>沪A30260D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -10503,12 +10515,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10522,7 +10534,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10571,22 +10583,22 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10624,7 +10636,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10638,7 +10650,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10673,12 +10685,12 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10691,7 +10703,7 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A30829D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -10701,7 +10713,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -10739,12 +10751,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10758,7 +10770,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10807,7 +10819,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A35683D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10817,7 +10829,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10855,12 +10867,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10874,7 +10886,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10899,18 +10911,22 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB86" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10939,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A51582D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10933,7 +10949,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10971,12 +10987,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10990,7 +11006,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -11015,22 +11031,18 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11055,7 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A50235D</t>
+          <t>沪A35683D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -11053,7 +11065,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -11091,12 +11103,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11110,7 +11122,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11135,22 +11147,18 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC88" s="2" t="inlineStr">
-        <is>
-          <t>98.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11171,7 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51582D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -11173,7 +11181,7 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -11211,12 +11219,12 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11230,7 +11238,7 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="W89" s="2" t="inlineStr">
@@ -11265,12 +11273,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11283,22 +11291,22 @@
       <c r="B90" s="2" t="inlineStr"/>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A50235D</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>09:40</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -11331,12 +11339,12 @@
       <c r="N90" s="2" t="inlineStr"/>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11350,7 +11358,7 @@
       <c r="U90" s="2" t="inlineStr"/>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
@@ -11385,12 +11393,12 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>98.0</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11403,22 +11411,22 @@
       <c r="B91" s="2" t="inlineStr"/>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -11451,12 +11459,12 @@
       <c r="N91" s="2" t="inlineStr"/>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11470,7 +11478,7 @@
       <c r="U91" s="2" t="inlineStr"/>
       <c r="V91" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W91" s="2" t="inlineStr">
@@ -11505,12 +11513,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11523,7 +11531,7 @@
       <c r="B92" s="2" t="inlineStr"/>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -11533,7 +11541,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11576,7 +11584,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11590,7 +11598,7 @@
       <c r="U92" s="2" t="inlineStr"/>
       <c r="V92" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="W92" s="2" t="inlineStr">
@@ -11625,12 +11633,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11651,7 @@
       <c r="B93" s="2" t="inlineStr"/>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -11653,7 +11661,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11691,12 +11699,12 @@
       <c r="N93" s="2" t="inlineStr"/>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11710,47 +11718,287 @@
       <c r="U93" s="2" t="inlineStr"/>
       <c r="V93" s="2" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="W93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X93" s="2" t="inlineStr">
+      <c r="X95" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z93" s="2" t="inlineStr">
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AA95" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
+      <c r="AB95" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="AD93" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-operations.xlsx
+++ b/data/export/2026-10-31-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5308,12 +5308,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9024,12 +9024,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -9201,24 +9201,24 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9325,24 +9325,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
@@ -9439,32 +9439,36 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9472,7 +9476,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9496,17 +9500,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9516,12 +9520,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9559,32 +9563,36 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -9592,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9616,17 +9624,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9636,12 +9644,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9679,32 +9687,36 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -9712,7 +9724,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9736,17 +9748,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9756,12 +9768,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9832,7 +9844,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9881,7 +9893,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9952,7 +9964,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9996,12 +10008,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10130,7 +10142,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10373,7 +10385,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10502,7 +10514,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -10626,7 +10638,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10708,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10750,7 +10762,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10886,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10998,7 +11010,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11134,7 @@
       </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11204,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11316,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11360,17 +11372,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11518,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -11576,7 +11588,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11620,17 +11632,17 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11762,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11820,7 +11832,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11864,17 +11876,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11956,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11998,7 +12010,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12134,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12232,17 +12244,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12324,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12436,7 +12448,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12610,7 +12622,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12920,7 +12932,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13098,7 +13110,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -13222,7 +13234,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13416,7 +13428,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13470,7 +13482,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13540,7 +13552,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13589,7 +13601,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD106" s="2" t="inlineStr">
@@ -13718,7 +13730,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13842,7 +13854,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13978,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14102,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14172,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14214,7 +14226,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14482,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14548,7 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q114" s="2" t="inlineStr">
@@ -14580,17 +14592,17 @@
       </c>
       <c r="AB114" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC114" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14672,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14704,17 +14716,17 @@
       </c>
       <c r="AB115" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -14784,7 +14796,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14962,7 +14974,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15044,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15076,17 +15088,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15168,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15210,7 +15222,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15292,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15324,17 +15336,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -15458,7 +15470,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15540,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15652,7 +15664,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15776,7 +15788,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15954,7 +15966,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -16078,7 +16090,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -16202,7 +16214,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16284,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16326,7 +16338,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -16450,7 +16462,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16586,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -16830,7 +16842,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16966,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17090,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -17148,7 +17160,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17202,7 +17214,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -17326,7 +17338,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -17396,7 +17408,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17440,17 +17452,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -17574,7 +17586,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17656,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17822,7 +17834,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -17946,7 +17958,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -18070,7 +18082,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -18194,7 +18206,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -18558,7 +18570,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -18814,7 +18826,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -19000,7 +19012,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19044,17 +19056,17 @@
       </c>
       <c r="AB150" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC150" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -19124,7 +19136,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19173,12 +19185,12 @@
       </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -19248,7 +19260,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19292,17 +19304,17 @@
       </c>
       <c r="AB152" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -19372,7 +19384,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19426,7 +19438,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -19496,7 +19508,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19540,17 +19552,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -19620,7 +19632,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19744,7 +19756,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19793,7 +19805,7 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19868,7 +19880,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19922,7 +19934,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -19992,7 +20004,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20046,7 +20058,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20182,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -20240,7 +20252,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20418,7 +20430,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -20542,7 +20554,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -20612,7 +20624,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20666,7 +20678,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -20786,7 +20798,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -20910,7 +20922,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -21158,7 +21170,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -21282,7 +21294,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -21402,7 +21414,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -21596,7 +21608,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21799,32 +21811,36 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -21832,7 +21848,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21856,17 +21872,17 @@
       </c>
       <c r="X173" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z173" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA173" s="2" t="inlineStr">
@@ -21876,17 +21892,17 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -21929,24 +21945,24 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
@@ -21956,7 +21972,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22005,12 +22021,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -22043,32 +22059,36 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
           <t>06:32</t>
@@ -22076,7 +22096,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22100,17 +22120,17 @@
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA175" s="2" t="inlineStr">
@@ -22120,17 +22140,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>133.5</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -22163,12 +22183,12 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq29推进至seq62，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -22196,7 +22216,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22204,10 +22224,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R176" s="2" t="inlineStr"/>
-      <c r="S176" s="2" t="inlineStr"/>
-      <c r="T176" s="2" t="inlineStr"/>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置锦绣路花木路 ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V176" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22293,24 +22329,24 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O177" s="2" t="inlineStr">
@@ -22320,7 +22356,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22369,7 +22405,7 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
@@ -22407,32 +22443,36 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N178" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -22440,7 +22480,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22464,17 +22504,17 @@
       </c>
       <c r="X178" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y178" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z178" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA178" s="2" t="inlineStr">
@@ -22484,17 +22524,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -22560,7 +22600,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22614,7 +22654,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -22647,12 +22687,12 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -22680,7 +22720,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22688,10 +22728,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R180" s="2" t="inlineStr"/>
-      <c r="S180" s="2" t="inlineStr"/>
-      <c r="T180" s="2" t="inlineStr"/>
-      <c r="U180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V180" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -22734,7 +22790,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -22767,32 +22823,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:37</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22800,7 +22860,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22824,17 +22884,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22844,17 +22904,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -22920,7 +22980,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -22974,7 +23034,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -23040,7 +23100,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23160,7 +23220,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23280,7 +23340,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23334,7 +23394,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -23400,7 +23460,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23574,7 +23634,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -24140,7 +24200,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24189,7 +24249,7 @@
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
@@ -24442,7 +24502,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -24512,7 +24572,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24561,7 +24621,7 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
@@ -24636,7 +24696,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24685,12 +24745,12 @@
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -25000,7 +25060,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25054,7 +25114,7 @@
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -25298,7 +25358,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25552,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25536,17 +25596,17 @@
       </c>
       <c r="AB203" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25612,7 +25672,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25661,7 +25721,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25736,7 +25796,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25780,17 +25840,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -25856,7 +25916,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25900,17 +25960,17 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -26158,7 +26218,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -26228,7 +26288,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26277,7 +26337,7 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26472,7 +26532,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26521,12 +26581,12 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -26890,7 +26950,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -26956,7 +27016,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q215" s="2" t="inlineStr">
@@ -27010,7 +27070,7 @@
       </c>
       <c r="AD215" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -27080,7 +27140,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27129,7 +27189,7 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27204,7 +27264,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27248,17 +27308,17 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27328,7 +27388,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27372,17 +27432,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -27506,7 +27566,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -27572,7 +27632,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27616,17 +27676,17 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -27696,7 +27756,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27745,12 +27805,12 @@
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -28060,7 +28120,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28114,7 +28174,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -28304,7 +28364,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28348,17 +28408,17 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28478,7 +28538,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -28548,7 +28608,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28592,17 +28652,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -28668,7 +28728,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q229" s="2" t="inlineStr">
@@ -28712,17 +28772,17 @@
       </c>
       <c r="AB229" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC229" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -28916,7 +28976,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -28960,17 +29020,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -29342,7 +29402,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -29532,7 +29592,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29576,17 +29636,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -29656,7 +29716,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29705,7 +29765,7 @@
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
@@ -29780,7 +29840,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29824,17 +29884,17 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -29904,7 +29964,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -29953,12 +30013,12 @@
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -30400,7 +30460,7 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q243" s="2" t="inlineStr">
@@ -30454,7 +30514,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -30648,7 +30708,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30692,17 +30752,17 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30826,7 +30886,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -30896,7 +30956,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -30945,7 +31005,7 @@
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
@@ -31020,7 +31080,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31069,7 +31129,7 @@
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
@@ -31144,7 +31204,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31188,17 +31248,17 @@
       </c>
       <c r="AB249" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -31268,7 +31328,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31317,12 +31377,12 @@
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31388,7 +31448,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31432,17 +31492,17 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -31628,7 +31688,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31672,17 +31732,17 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -32050,7 +32110,7 @@
       </c>
       <c r="AD256" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -32120,7 +32180,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q257" s="2" t="inlineStr">
@@ -32174,7 +32234,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -32368,7 +32428,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32412,17 +32472,17 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -32546,7 +32606,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -32736,7 +32796,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32785,7 +32845,7 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
@@ -32860,7 +32920,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32909,7 +32969,7 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -32980,7 +33040,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33024,17 +33084,17 @@
       </c>
       <c r="AB264" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -33104,7 +33164,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33148,17 +33208,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -33228,7 +33288,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33277,12 +33337,12 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -33352,7 +33412,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33396,17 +33456,17 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -33898,7 +33958,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -33968,7 +34028,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34022,7 +34082,7 @@
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -34216,7 +34276,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34260,17 +34320,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -34518,7 +34578,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -34561,24 +34621,24 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O277" s="2" t="inlineStr">
@@ -34588,7 +34648,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34637,7 +34697,7 @@
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
@@ -34685,12 +34745,12 @@
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr"/>
@@ -34712,7 +34772,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34761,7 +34821,7 @@
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
@@ -34799,32 +34859,36 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O279" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -34832,7 +34896,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34856,17 +34920,17 @@
       </c>
       <c r="X279" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA279" s="2" t="inlineStr">
@@ -34876,17 +34940,17 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -35126,7 +35190,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -35169,24 +35233,24 @@
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr"/>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N282" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O282" s="2" t="inlineStr">
@@ -35196,7 +35260,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35245,12 +35309,12 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35283,32 +35347,36 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N283" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O283" s="2" t="inlineStr">
         <is>
           <t>08:41</t>
@@ -35316,7 +35384,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35340,17 +35408,17 @@
       </c>
       <c r="X283" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA283" s="2" t="inlineStr">
@@ -35360,17 +35428,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -35403,32 +35471,36 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr"/>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N284" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O284" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -35436,7 +35508,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35460,17 +35532,17 @@
       </c>
       <c r="X284" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y284" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z284" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA284" s="2" t="inlineStr">
@@ -35480,17 +35552,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -35556,7 +35628,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35610,7 +35682,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -35643,32 +35715,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>08:31</t>
@@ -35676,7 +35752,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35700,17 +35776,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35720,17 +35796,17 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -35796,7 +35872,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35840,17 +35916,17 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -35916,7 +35992,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -35960,17 +36036,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-31-operations.xlsx
+++ b/data/export/2026-10-31-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9272,12 +9272,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9811,32 +9811,36 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9844,7 +9848,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9868,17 +9872,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9888,12 +9892,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9931,32 +9935,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9964,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9988,17 +9996,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10008,12 +10016,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10142,7 +10150,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10638,7 +10646,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10716,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10752,12 +10760,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
@@ -11010,7 +11018,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11212,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11762,7 +11770,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11956,7 +11964,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12134,7 +12142,7 @@
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12208,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12249,12 +12257,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12332,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12448,7 +12456,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12492,17 +12500,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13234,7 +13242,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13436,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13482,7 +13490,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13738,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14180,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14216,12 +14224,12 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
@@ -14482,7 +14490,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14804,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14974,7 +14982,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15176,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15292,7 +15300,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15341,12 +15349,12 @@
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15478,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15548,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15584,17 +15592,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15672,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -16090,7 +16098,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -16284,7 +16292,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16338,7 +16346,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -16586,7 +16594,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16850,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -17090,7 +17098,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -17338,7 +17346,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -17656,7 +17664,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17700,17 +17708,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17842,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -18206,7 +18214,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -19190,7 +19198,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19516,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19557,12 +19565,12 @@
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -19880,7 +19888,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19934,7 +19942,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -20004,7 +20012,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20048,12 +20056,12 @@
       </c>
       <c r="AB158" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
@@ -20252,7 +20260,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20430,7 +20438,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -20624,7 +20632,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20798,7 +20806,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -20922,7 +20930,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -21608,7 +21616,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -22026,7 +22034,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -22692,7 +22700,7 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
@@ -22720,7 +22728,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22790,7 +22798,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22833,24 +22841,24 @@
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>21:37</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N181" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O181" s="2" t="inlineStr">
@@ -22860,7 +22868,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22909,12 +22917,12 @@
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -22947,32 +22955,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -22980,7 +22992,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23004,17 +23016,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -23024,12 +23036,12 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>134.8</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
@@ -23067,32 +23079,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23100,7 +23116,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23124,17 +23140,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23144,17 +23160,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -23220,7 +23236,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23340,7 +23356,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23460,7 +23476,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -24006,7 +24022,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -24750,7 +24766,7 @@
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25250,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25552,7 +25568,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25601,12 +25617,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -25796,7 +25812,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25840,12 +25856,12 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
@@ -26586,7 +26602,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -26706,7 +26722,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27264,7 +27280,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27313,12 +27329,12 @@
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -27632,7 +27648,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27676,12 +27692,12 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -27810,7 +27826,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -28364,7 +28380,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28413,12 +28429,12 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -28608,7 +28624,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28652,12 +28668,12 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -28976,7 +28992,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29526,7 +29542,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -29840,7 +29856,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -30018,7 +30034,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -30638,7 +30654,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30708,7 +30724,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30757,12 +30773,12 @@
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31382,7 +31398,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -31448,7 +31464,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31492,12 +31508,12 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
@@ -31688,7 +31704,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -32428,7 +32444,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32477,12 +32493,12 @@
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -32730,7 +32746,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -33164,7 +33180,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33208,12 +33224,12 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
@@ -33342,7 +33358,7 @@
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -33412,7 +33428,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -34276,7 +34292,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34325,12 +34341,12 @@
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -34454,7 +34470,7 @@
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -35314,7 +35330,7 @@
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -35384,7 +35400,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35428,12 +35444,12 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
@@ -35508,7 +35524,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35725,24 +35741,24 @@
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N286" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O286" s="2" t="inlineStr">
@@ -35752,7 +35768,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35801,12 +35817,12 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35839,32 +35855,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>08:41</t>
@@ -35872,7 +35892,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35896,17 +35916,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35916,12 +35936,12 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
@@ -35992,7 +36012,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
